--- a/MATH/M02/bus123-math-m02-l01-starter.xlsx
+++ b/MATH/M02/bus123-math-m02-l01-starter.xlsx
@@ -2,9 +2,6 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="780" windowWidth="23840" windowHeight="15060" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" state="visible" r:id="rId2"/>
@@ -12,113 +9,96 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="23">
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="2"/>
+  <fonts count="26">
+    <font>
+      <name val="Calibri"/>
       <color theme="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="16"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <i val="1"/>
       <color rgb="FFD4A052"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <b val="1"/>
       <color rgb="FF0C1A2E"/>
       <sz val="13"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <color rgb="FF1A1A2E"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <b val="1"/>
       <color rgb="FF1B2E48"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <color rgb="FF1A1A2E"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <i val="1"/>
       <color rgb="FF1B4D35"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="15"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <i val="1"/>
       <color rgb="FF1B2E48"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <b val="1"/>
       <color rgb="FF1B6B3A"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="14"/>
@@ -126,50 +106,67 @@
     <font>
       <name val="Aptos Display"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="18"/>
     </font>
     <font>
       <name val="Aptos"/>
       <b val="1"/>
-      <color rgb="004A7C5E"/>
+      <color rgb="FF4A7C5E"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Aptos"/>
       <b val="1"/>
-      <color rgb="001A1F2C"/>
+      <color rgb="FF1A1F2C"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Aptos"/>
       <i val="1"/>
-      <color rgb="004A5567"/>
+      <color rgb="FF4A5567"/>
     </font>
     <font>
       <name val="Aptos"/>
       <i val="1"/>
-      <color rgb="004A5567"/>
+      <color rgb="FF4A5567"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Aptos"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Aptos"/>
-      <color rgb="001A1F2C"/>
+      <color rgb="FF1A1F2C"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Aptos"/>
       <b val="1"/>
-      <color rgb="004A7C5E"/>
+      <color rgb="FF4A7C5E"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFB8843D"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF1A1F2C"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF355773"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="26">
     <fill>
       <patternFill/>
     </fill>
@@ -179,101 +176,126 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0C1A2E"/>
-        <bgColor rgb="FF1A1A2E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1B2E48"/>
-        <bgColor rgb="FF1A1A2E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF0F7F4"/>
-        <bgColor rgb="FFEEF4FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFF0F7F4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD6F0E4"/>
-        <bgColor rgb="FFE8F5E9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD4A052"/>
-        <bgColor rgb="FFFF8080"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFD966"/>
-        <bgColor rgb="FFFFFF99"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8F5E9"/>
-        <bgColor rgb="FFF0F7F4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEEF4FF"/>
-        <bgColor rgb="FFF0F7F4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000E1116"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2EEE5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00355773"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3C4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EAF3EC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FAF8F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0E1116"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2EEE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF355773"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF3C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF3EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAF8F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0E1116"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF3EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2EEE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0E1116"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF3EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2EEE5"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="8">
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FFD0D0D0"/>
@@ -287,65 +309,69 @@
       <bottom style="thin">
         <color rgb="FFD0D0D0"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FFD0D0D0"/>
       </left>
-      <right/>
       <top style="thin">
         <color rgb="FFD0D0D0"/>
       </top>
       <bottom style="thin">
         <color rgb="FFD0D0D0"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color rgb="FFD0D0D0"/>
       </top>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color rgb="FFD0D0D0"/>
       </top>
       <bottom style="thin">
         <color rgb="FFD0D0D0"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <bottom style="thin">
-        <color rgb="00E5E1D6"/>
+        <color rgb="FFE5E1D6"/>
       </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00E5E1D6"/>
+        <color rgb="FFE5E1D6"/>
       </left>
       <right style="thin">
-        <color rgb="00E5E1D6"/>
+        <color rgb="FFE5E1D6"/>
       </right>
       <top style="thin">
-        <color rgb="00E5E1D6"/>
+        <color rgb="FFE5E1D6"/>
       </top>
       <bottom style="thin">
-        <color rgb="00E5E1D6"/>
+        <color rgb="FFE5E1D6"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE5E1D6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE5E1D6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE5E1D6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE5E1D6"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -444,40 +470,29 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -488,11 +503,51 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -565,7 +620,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -607,17 +662,17 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -666,13 +721,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
@@ -736,8 +791,6 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -751,21 +804,21 @@
   <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="78" customWidth="1" min="3" max="3"/>
-    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" style="35" min="1" max="1"/>
+    <col width="24" customWidth="1" style="35" min="2" max="2"/>
+    <col width="78" customWidth="1" style="35" min="3" max="3"/>
+    <col width="4" customWidth="1" style="35" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="32" customHeight="1" s="35">
       <c r="A1" s="28" t="inlineStr">
         <is>
           <t>BUS123 · Math Track · M02 · L01 — Solving Equations</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="27.75" customHeight="1"/>
-    <row r="3" ht="21.75" customHeight="1">
+    <row r="2" ht="27.75" customHeight="1" s="35"/>
+    <row r="3" ht="21.75" customHeight="1" s="35">
       <c r="A3" s="13" t="n"/>
       <c r="B3" s="29" t="inlineStr">
         <is>
@@ -773,51 +826,51 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="9.75" customHeight="1"/>
-    <row r="5" ht="21.75" customHeight="1">
+    <row r="4" ht="9.75" customHeight="1" s="35"/>
+    <row r="5" ht="21.75" customHeight="1" s="35">
       <c r="B5" s="30" t="inlineStr">
         <is>
           <t>Learning Objectives</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="19.5" customHeight="1">
+    <row r="6" ht="19.5" customHeight="1" s="35">
       <c r="B6" s="11" t="inlineStr">
         <is>
           <t>- Solve one-step equations using inverse operations</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="19.5" customHeight="1">
+    <row r="7" ht="19.5" customHeight="1" s="35">
       <c r="B7" s="10" t="inlineStr">
         <is>
           <t>- Solve two-step equations by reversing the order of operations</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="19.5" customHeight="1">
+    <row r="8" ht="19.5" customHeight="1" s="35">
       <c r="B8" s="11" t="inlineStr">
         <is>
           <t>- Collect variable terms to solve equations with variables on both sides</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="19.5" customHeight="1">
+    <row r="9" ht="19.5" customHeight="1" s="35">
       <c r="B9" s="10" t="inlineStr">
         <is>
           <t>- Rearrange multi-variable formulas to isolate any target variable</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="9.75" customHeight="1"/>
-    <row r="11" ht="21.75" customHeight="1">
+    <row r="10" ht="9.75" customHeight="1" s="35"/>
+    <row r="11" ht="21.75" customHeight="1" s="35">
       <c r="B11" s="30" t="inlineStr">
         <is>
           <t>How to Use This Workbook</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="19.5" customHeight="1">
+    <row r="12" ht="19.5" customHeight="1" s="35">
       <c r="B12" s="31" t="inlineStr">
         <is>
           <t>Yellow cells</t>
@@ -829,7 +882,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="19.5" customHeight="1">
+    <row r="13" ht="19.5" customHeight="1" s="35">
       <c r="B13" s="31" t="inlineStr">
         <is>
           <t>Live You Try It</t>
@@ -841,7 +894,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="19.5" customHeight="1">
+    <row r="14" ht="19.5" customHeight="1" s="35">
       <c r="B14" s="31" t="inlineStr">
         <is>
           <t>Class Challenge</t>
@@ -853,7 +906,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="19.5" customHeight="1">
+    <row r="15" ht="19.5" customHeight="1" s="35">
       <c r="B15" s="31" t="inlineStr">
         <is>
           <t>FormulaReferenceCard</t>
@@ -865,26 +918,25 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="19.5" customHeight="1">
+    <row r="16" ht="19.5" customHeight="1" s="35">
       <c r="B16" s="15" t="n"/>
       <c r="C16" s="16" t="n"/>
     </row>
-    <row r="17" ht="9.75" customHeight="1"/>
-    <row r="18" ht="18" customHeight="1">
+    <row r="17" ht="9.75" customHeight="1" s="35"/>
+    <row r="18" ht="18" customHeight="1" s="35">
       <c r="B18" s="33" t="inlineStr">
         <is>
           <t>TIP: Write the equation setup before solving. Live You Try It gives hints and feedback; Class Challenge is the submitted next-level work.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1"/>
-    <row r="20" ht="18" customHeight="1"/>
+    <row r="19" ht="18" customHeight="1" s="35"/>
+    <row r="20" ht="18" customHeight="1" s="35"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -897,66 +949,33 @@
   <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="3" customWidth="1" style="35" min="1" max="1"/>
+    <col width="7" customWidth="1" style="35" min="2" max="2"/>
+    <col width="48" customWidth="1" style="35" min="3" max="3"/>
+    <col width="23" customWidth="1" style="35" min="4" max="4"/>
+    <col width="23" customWidth="1" style="35" min="5" max="5"/>
+    <col width="15" customWidth="1" style="35" min="6" max="6"/>
+    <col width="34" customWidth="1" style="35" min="7" max="7"/>
+    <col width="32" customWidth="1" style="35" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="30" customHeight="1" s="35">
       <c r="A1" s="34" t="inlineStr">
         <is>
           <t>M02 · L01 — Live You Try It | Anchor &amp; Oak Events</t>
         </is>
       </c>
-      <c r="B1" s="35" t="n"/>
-      <c r="C1" s="35" t="n"/>
-      <c r="D1" s="35" t="n"/>
-      <c r="E1" s="35" t="n"/>
-      <c r="F1" s="35" t="n"/>
-      <c r="G1" s="35" t="n"/>
-      <c r="H1" s="35" t="n"/>
-    </row>
-    <row r="2" ht="42" customHeight="1">
+    </row>
+    <row r="2" ht="42" customHeight="1" s="35">
       <c r="A2" s="36" t="inlineStr">
         <is>
           <t>Self-graded Excel pauses. Use the exact numbers from the slides, type your setup/work, and let the feedback cell help you revise.</t>
         </is>
       </c>
-      <c r="B2" s="35" t="n"/>
-      <c r="C2" s="35" t="n"/>
-      <c r="D2" s="35" t="n"/>
-      <c r="E2" s="35" t="n"/>
-      <c r="F2" s="35" t="n"/>
-      <c r="G2" s="35" t="n"/>
-      <c r="H2" s="35" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="35" t="n"/>
-      <c r="B3" s="35" t="n"/>
-      <c r="C3" s="35" t="n"/>
-      <c r="D3" s="35" t="n"/>
-      <c r="E3" s="35" t="n"/>
-      <c r="F3" s="35" t="n"/>
-      <c r="G3" s="35" t="n"/>
-      <c r="H3" s="35" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="35" t="n"/>
-      <c r="B4" s="35" t="n"/>
-      <c r="C4" s="35" t="n"/>
-      <c r="D4" s="35" t="n"/>
-      <c r="E4" s="35" t="n"/>
-      <c r="F4" s="35" t="n"/>
-      <c r="G4" s="35" t="n"/>
-      <c r="H4" s="35" t="n"/>
-    </row>
+    </row>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5">
-      <c r="A5" s="35" t="n"/>
       <c r="B5" s="37" t="inlineStr">
         <is>
           <t>#</t>
@@ -993,8 +1012,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="68" customHeight="1">
-      <c r="A6" s="35" t="n"/>
+    <row r="6" ht="68" customHeight="1" s="35">
       <c r="B6" s="38" t="n">
         <v>1</v>
       </c>
@@ -1016,8 +1034,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="68" customHeight="1">
-      <c r="A7" s="35" t="n"/>
+    <row r="7" ht="68" customHeight="1" s="35">
       <c r="B7" s="41" t="n">
         <v>2</v>
       </c>
@@ -1039,8 +1056,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="68" customHeight="1">
-      <c r="A8" s="35" t="n"/>
+    <row r="8" ht="68" customHeight="1" s="35">
       <c r="B8" s="38" t="n">
         <v>3</v>
       </c>
@@ -1062,8 +1078,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="68" customHeight="1">
-      <c r="A9" s="35" t="n"/>
+    <row r="9" ht="68" customHeight="1" s="35">
       <c r="B9" s="41" t="n">
         <v>4</v>
       </c>
@@ -1085,8 +1100,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="68" customHeight="1">
-      <c r="A10" s="35" t="n"/>
+    <row r="10" ht="68" customHeight="1" s="35">
       <c r="B10" s="38" t="n">
         <v>5</v>
       </c>
@@ -1108,18 +1122,8 @@
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="35" t="n"/>
-      <c r="B11" s="35" t="n"/>
-      <c r="C11" s="35" t="n"/>
-      <c r="D11" s="35" t="n"/>
-      <c r="E11" s="35" t="n"/>
-      <c r="F11" s="35" t="n"/>
-      <c r="G11" s="35" t="n"/>
-      <c r="H11" s="35" t="n"/>
-    </row>
+    <row r="11"/>
     <row r="12">
-      <c r="A12" s="35" t="n"/>
       <c r="B12" s="42" t="inlineStr">
         <is>
           <t>Self-check score</t>
@@ -1129,18 +1133,13 @@
         <f>COUNTIF(H6:H10,"Correct*")&amp;" of 5 complete"</f>
         <v/>
       </c>
-      <c r="D12" s="35" t="n"/>
-      <c r="E12" s="35" t="n"/>
-      <c r="F12" s="35" t="n"/>
-      <c r="G12" s="35" t="n"/>
-      <c r="H12" s="35" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1153,61 +1152,32 @@
   <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="54" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="3" customWidth="1" style="35" min="1" max="1"/>
+    <col width="8" customWidth="1" style="35" min="2" max="2"/>
+    <col width="54" customWidth="1" style="35" min="3" max="3"/>
+    <col width="24" customWidth="1" style="35" min="4" max="4"/>
+    <col width="24" customWidth="1" style="35" min="5" max="5"/>
+    <col width="15" customWidth="1" style="35" min="6" max="6"/>
+    <col width="24" customWidth="1" style="35" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="30" customHeight="1" s="35">
       <c r="A1" s="34" t="inlineStr">
         <is>
           <t>M02 · L01 — Class Challenge | Anchor &amp; Oak Events</t>
         </is>
       </c>
-      <c r="B1" s="35" t="n"/>
-      <c r="C1" s="35" t="n"/>
-      <c r="D1" s="35" t="n"/>
-      <c r="E1" s="35" t="n"/>
-      <c r="F1" s="35" t="n"/>
-      <c r="G1" s="35" t="n"/>
-    </row>
-    <row r="2" ht="42" customHeight="1">
+    </row>
+    <row r="2" ht="42" customHeight="1" s="35">
       <c r="A2" s="36" t="inlineStr">
         <is>
           <t>Graded or next-level activity. Choose the setup, build the Excel work, and enter the final answer. Use slide numbers, but expect one extra reasoning step.</t>
         </is>
       </c>
-      <c r="B2" s="35" t="n"/>
-      <c r="C2" s="35" t="n"/>
-      <c r="D2" s="35" t="n"/>
-      <c r="E2" s="35" t="n"/>
-      <c r="F2" s="35" t="n"/>
-      <c r="G2" s="35" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="35" t="n"/>
-      <c r="B3" s="35" t="n"/>
-      <c r="C3" s="35" t="n"/>
-      <c r="D3" s="35" t="n"/>
-      <c r="E3" s="35" t="n"/>
-      <c r="F3" s="35" t="n"/>
-      <c r="G3" s="35" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="35" t="n"/>
-      <c r="B4" s="35" t="n"/>
-      <c r="C4" s="35" t="n"/>
-      <c r="D4" s="35" t="n"/>
-      <c r="E4" s="35" t="n"/>
-      <c r="F4" s="35" t="n"/>
-      <c r="G4" s="35" t="n"/>
-    </row>
+    </row>
+    <row r="3"/>
+    <row r="4"/>
     <row r="5">
-      <c r="A5" s="35" t="n"/>
       <c r="B5" s="37" t="inlineStr">
         <is>
           <t>#</t>
@@ -1239,8 +1209,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="72" customHeight="1">
-      <c r="A6" s="35" t="n"/>
+    <row r="6" ht="72" customHeight="1" s="35">
       <c r="B6" s="38" t="inlineStr">
         <is>
           <t>C1</t>
@@ -1260,8 +1229,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="72" customHeight="1">
-      <c r="A7" s="35" t="n"/>
+    <row r="7" ht="72" customHeight="1" s="35">
       <c r="B7" s="41" t="inlineStr">
         <is>
           <t>C2</t>
@@ -1281,8 +1249,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="72" customHeight="1">
-      <c r="A8" s="35" t="n"/>
+    <row r="8" ht="72" customHeight="1" s="35">
       <c r="B8" s="38" t="inlineStr">
         <is>
           <t>C3</t>
@@ -1302,8 +1269,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="72" customHeight="1">
-      <c r="A9" s="35" t="n"/>
+    <row r="9" ht="72" customHeight="1" s="35">
       <c r="B9" s="41" t="inlineStr">
         <is>
           <t>C4</t>
@@ -1323,8 +1289,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="72" customHeight="1">
-      <c r="A10" s="35" t="n"/>
+    <row r="10" ht="72" customHeight="1" s="35">
       <c r="B10" s="38" t="inlineStr">
         <is>
           <t>C5</t>
@@ -1344,8 +1309,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="72" customHeight="1">
-      <c r="A11" s="35" t="n"/>
+    <row r="11" ht="72" customHeight="1" s="35">
       <c r="B11" s="41" t="inlineStr">
         <is>
           <t>C6</t>
@@ -1370,7 +1334,7 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1381,240 +1345,160 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="3" customWidth="1" min="6" max="6"/>
+    <col width="21.11000061035156" customWidth="1" style="35" min="1" max="1"/>
+    <col width="25.55999946594238" customWidth="1" style="35" min="2" max="2"/>
+    <col width="34.43999862670898" customWidth="1" style="35" min="3" max="3"/>
+    <col width="33.33000183105469" customWidth="1" style="35" min="4" max="4"/>
+    <col width="28" customWidth="1" style="35" min="5" max="5"/>
+    <col width="3" customWidth="1" style="35" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Formula Reference Card — M02 · L01 · Solving Equations</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="25.5" customHeight="1"/>
-    <row r="3" ht="7.5" customHeight="1"/>
-    <row r="4" ht="19.5" customHeight="1">
-      <c r="B4" s="24" t="inlineStr">
-        <is>
-          <t>Equation Type</t>
-        </is>
-      </c>
-      <c r="C4" s="24" t="inlineStr">
-        <is>
-          <t>Standard Form</t>
-        </is>
-      </c>
-      <c r="D4" s="24" t="inlineStr">
-        <is>
-          <t>Solving Steps</t>
-        </is>
-      </c>
-      <c r="E4" s="24" t="inlineStr">
-        <is>
-          <t>Business Example</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="63.75" customHeight="1">
-      <c r="B5" s="25" t="inlineStr">
-        <is>
-          <t>One-Step (add/sub)</t>
-        </is>
-      </c>
-      <c r="C5" s="25" t="inlineStr">
-        <is>
-          <t>x + a = b
-or x – a = b</t>
-        </is>
-      </c>
-      <c r="D5" s="25" t="inlineStr">
-        <is>
-          <t>1. Move constant to right side
-2. Add or subtract both sides
-3. Answer: x = b – a</t>
-        </is>
-      </c>
-      <c r="E5" s="43" t="inlineStr">
-        <is>
-          <t>x + 1650 = 4200
-x = 4200 – 1650 = 2550</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="63.75" customHeight="1">
-      <c r="B6" s="26" t="inlineStr">
-        <is>
-          <t>One-Step (mult/div)</t>
-        </is>
-      </c>
-      <c r="C6" s="26" t="inlineStr">
-        <is>
-          <t>ax = b
-or x/a = b</t>
-        </is>
-      </c>
-      <c r="D6" s="26" t="inlineStr">
-        <is>
-          <t>1. Divide (or multiply) both sides by a
-2. Answer: x = b / a</t>
-        </is>
-      </c>
-      <c r="E6" s="44" t="inlineStr">
-        <is>
-          <t>60x = 4080
-x = 4080/60 = 68</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="63.75" customHeight="1">
-      <c r="B7" s="25" t="inlineStr">
-        <is>
-          <t>Two-Step</t>
-        </is>
-      </c>
-      <c r="C7" s="25" t="inlineStr">
-        <is>
-          <t>ax + b = c</t>
-        </is>
-      </c>
-      <c r="D7" s="25" t="inlineStr">
-        <is>
-          <t>1. Subtract b from both sides
-2. Divide both sides by a
-3. Answer: x = (c – b) / a</t>
-        </is>
-      </c>
-      <c r="E7" s="43" t="inlineStr">
-        <is>
-          <t>8x + 120 = 1240
-8x = 1120 → x = 140</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="63.75" customHeight="1">
-      <c r="B8" s="26" t="inlineStr">
-        <is>
-          <t>Variables Both Sides</t>
-        </is>
-      </c>
-      <c r="C8" s="26" t="inlineStr">
-        <is>
-          <t>ax + b = cx + d</t>
-        </is>
-      </c>
-      <c r="D8" s="26" t="inlineStr">
-        <is>
-          <t>1. Subtract smaller variable term from both sides
-2. Collect constants
-3. Divide by coefficient</t>
-        </is>
-      </c>
-      <c r="E8" s="44" t="inlineStr">
-        <is>
-          <t>500+25g = 200+40g
-300 = 15g → g = 20</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="63.75" customHeight="1">
-      <c r="B9" s="25" t="inlineStr">
-        <is>
-          <t>Literal Equation</t>
-        </is>
-      </c>
-      <c r="C9" s="25" t="inlineStr">
-        <is>
-          <t>F(a, b, c) = result
-Solve for one variable</t>
-        </is>
-      </c>
-      <c r="D9" s="25" t="inlineStr">
-        <is>
-          <t>1. Treat all other variables as constants
-2. Apply inverse operations
-3. Isolate target variable</t>
-        </is>
-      </c>
-      <c r="E9" s="43" t="inlineStr">
-        <is>
-          <t>FC = R – VC
-FC = 18500–11200 = 7300</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="9.75" customHeight="1"/>
-    <row r="11" ht="21.75" customHeight="1">
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Golden Rules</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>RULE 1: Whatever you do to one side of an equation, you MUST do to the other side.</t>
-        </is>
-      </c>
-      <c r="C12" s="45" t="n"/>
-      <c r="D12" s="45" t="n"/>
-      <c r="E12" s="45" t="n"/>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="B13" s="27" t="inlineStr">
-        <is>
-          <t>RULE 2: For two-step equations — undo addition/subtraction BEFORE multiplication/division.</t>
-        </is>
-      </c>
-      <c r="C13" s="45" t="n"/>
-      <c r="D13" s="45" t="n"/>
-      <c r="E13" s="45" t="n"/>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>RULE 3: When variables appear on both sides — subtract the smaller coefficient first to keep it positive.</t>
-        </is>
-      </c>
-      <c r="C14" s="45" t="n"/>
-      <c r="D14" s="45" t="n"/>
-      <c r="E14" s="45" t="n"/>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="B15" s="27" t="inlineStr">
-        <is>
-          <t>RULE 4: In literal equations — treat every other variable as a constant and apply inverse operations normally.</t>
-        </is>
-      </c>
-      <c r="C15" s="45" t="n"/>
-      <c r="D15" s="45" t="n"/>
-      <c r="E15" s="45" t="n"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="46" t="inlineStr">
-        <is>
-          <t>Live You Try It answers use the same numbers as the slides. Class Challenge may combine two slide ideas in one prompt.</t>
-        </is>
-      </c>
-    </row>
+    <row r="1" ht="31.5" customHeight="1" s="35">
+      <c r="A1" s="60" t="inlineStr">
+        <is>
+          <t>Concept</t>
+        </is>
+      </c>
+      <c r="B1" s="60" t="inlineStr">
+        <is>
+          <t>Excel Pattern</t>
+        </is>
+      </c>
+      <c r="C1" s="60" t="inlineStr">
+        <is>
+          <t>Plain-English Meaning</t>
+        </is>
+      </c>
+      <c r="D1" s="60" t="inlineStr">
+        <is>
+          <t>Watch Out For</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="31.5" customHeight="1" s="35">
+      <c r="A2" s="64" t="inlineStr">
+        <is>
+          <t>One-step add/subtract</t>
+        </is>
+      </c>
+      <c r="B2" s="66" t="inlineStr">
+        <is>
+          <t>=4200-1650</t>
+        </is>
+      </c>
+      <c r="C2" s="64" t="inlineStr">
+        <is>
+          <t>Undo the constant to isolate the unknown.</t>
+        </is>
+      </c>
+      <c r="D2" s="67" t="inlineStr">
+        <is>
+          <t>Apply the same operation to both sides.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="31.5" customHeight="1" s="35">
+      <c r="A3" s="64" t="inlineStr">
+        <is>
+          <t>One-step multiply/divide</t>
+        </is>
+      </c>
+      <c r="B3" s="66" t="inlineStr">
+        <is>
+          <t>=4080/60</t>
+        </is>
+      </c>
+      <c r="C3" s="64" t="inlineStr">
+        <is>
+          <t>Divide by the coefficient to solve for the unit amount.</t>
+        </is>
+      </c>
+      <c r="D3" s="67" t="inlineStr">
+        <is>
+          <t>Keep the rate or coefficient in the denominator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="31.5" customHeight="1" s="35">
+      <c r="A4" s="64" t="inlineStr">
+        <is>
+          <t>Two-step equation</t>
+        </is>
+      </c>
+      <c r="B4" s="66" t="inlineStr">
+        <is>
+          <t>=(1240-120)/8</t>
+        </is>
+      </c>
+      <c r="C4" s="64" t="inlineStr">
+        <is>
+          <t>Remove the fixed amount, then divide by the variable rate.</t>
+        </is>
+      </c>
+      <c r="D4" s="67" t="inlineStr">
+        <is>
+          <t>Undo addition or subtraction before division.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="31.5" customHeight="1" s="35">
+      <c r="A5" s="64" t="inlineStr">
+        <is>
+          <t>Variables both sides</t>
+        </is>
+      </c>
+      <c r="B5" s="66" t="inlineStr">
+        <is>
+          <t>=(500-200)/(40-25)</t>
+        </is>
+      </c>
+      <c r="C5" s="64" t="inlineStr">
+        <is>
+          <t>Collect constants and divide by the difference in rates.</t>
+        </is>
+      </c>
+      <c r="D5" s="67" t="inlineStr">
+        <is>
+          <t>Subtract the smaller variable term first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="31.5" customHeight="1" s="35">
+      <c r="A6" s="64" t="inlineStr">
+        <is>
+          <t>Literal equation</t>
+        </is>
+      </c>
+      <c r="B6" s="66" t="inlineStr">
+        <is>
+          <t>=R-VC</t>
+        </is>
+      </c>
+      <c r="C6" s="64" t="inlineStr">
+        <is>
+          <t>Solve for the missing business measure using the known values.</t>
+        </is>
+      </c>
+      <c r="D6" s="67" t="inlineStr">
+        <is>
+          <t>Treat all other letters as constants.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="63.75" customHeight="1" s="35"/>
+    <row r="8" ht="63.75" customHeight="1" s="35"/>
+    <row r="9" ht="63.75" customHeight="1" s="35"/>
+    <row r="10" ht="9.75" customHeight="1" s="35"/>
+    <row r="11" ht="21.75" customHeight="1" s="35"/>
+    <row r="12" ht="24" customHeight="1" s="35"/>
+    <row r="13" ht="24" customHeight="1" s="35"/>
+    <row r="14" ht="24" customHeight="1" s="35"/>
+    <row r="15" ht="24" customHeight="1" s="35"/>
+    <row r="17"/>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="A1:F2"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B14:E14"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>